--- a/s60_signal/position-00386-600028.xlsx
+++ b/s60_signal/position-00386-600028.xlsx
@@ -1582,7 +1582,7 @@
     <t>2021-12-08</t>
   </si>
   <si>
-    <t>2021-12-14</t>
+    <t>2021-12-15</t>
   </si>
   <si>
     <t>2016-03-23</t>
@@ -87165,10 +87165,10 @@
         <v>1.023486622482049</v>
       </c>
       <c r="D1697" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E1697">
-        <v>1.171462706335121</v>
+        <v>1.168638418907111</v>
       </c>
       <c r="F1697">
         <v>1</v>
@@ -87177,10 +87177,10 @@
         <v>0.007276513377517952</v>
       </c>
       <c r="H1697">
-        <v>0.006948537293664879</v>
+        <v>0.007011361581092889</v>
       </c>
       <c r="I1697">
-        <v>0.1479760838530715</v>
+        <v>0.1451517964250617</v>
       </c>
       <c r="J1697">
         <v>0.8206071857002497</v>
@@ -87192,10 +87192,10 @@
         <v>4.15</v>
       </c>
       <c r="M1697">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N1697">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="O1697">
         <v>1</v>
@@ -87215,10 +87215,10 @@
         <v>1.005280550625046</v>
       </c>
       <c r="D1698" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E1698">
-        <v>1.171462706335121</v>
+        <v>1.168638418907111</v>
       </c>
       <c r="F1698">
         <v>1</v>
@@ -87227,10 +87227,10 @@
         <v>0.007274719449374954</v>
       </c>
       <c r="H1698">
-        <v>0.006948537293664879</v>
+        <v>0.007011361581092889</v>
       </c>
       <c r="I1698">
-        <v>0.1661821557100747</v>
+        <v>0.1633578682820649</v>
       </c>
       <c r="J1698">
         <v>0.8206071857002497</v>
@@ -87242,10 +87242,10 @@
         <v>4.14</v>
       </c>
       <c r="M1698">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="N1698">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="O1698">
         <v>1</v>
@@ -89065,10 +89065,10 @@
         <v>0.6908070802208526</v>
       </c>
       <c r="D1735" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1735">
-        <v>0.9439769405651197</v>
+        <v>0.8641052289704461</v>
       </c>
       <c r="F1735">
         <v>1</v>
@@ -89077,10 +89077,10 @@
         <v>0.007609192919779149</v>
       </c>
       <c r="H1735">
-        <v>0.00713602305943488</v>
+        <v>0.007255894771029553</v>
       </c>
       <c r="I1735">
-        <v>0.2531698603442671</v>
+        <v>0.1732981487495935</v>
       </c>
       <c r="J1735">
         <v>0.9079246508606686</v>
@@ -89092,10 +89092,10 @@
         <v>4.15</v>
       </c>
       <c r="M1735">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="N1735">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="O1735">
         <v>1</v>
@@ -90118,7 +90118,7 @@
         <v>522</v>
       </c>
       <c r="E1756">
-        <v>-0.6495643986389812</v>
+        <v>-0.6464949301644181</v>
       </c>
       <c r="F1756">
         <v>-1</v>
@@ -90127,10 +90127,10 @@
         <v>0.008496688749825796</v>
       </c>
       <c r="H1756">
-        <v>0.008969564398638982</v>
+        <v>0.00894649493016442</v>
       </c>
       <c r="I1756">
-        <v>0.2328756488131862</v>
+        <v>0.2298061803386231</v>
       </c>
       <c r="J1756">
         <v>1.306946847456245</v>
@@ -90142,10 +90142,10 @@
         <v>4.04</v>
       </c>
       <c r="M1756">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="N1756">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="O1756">
         <v>1</v>
@@ -90418,7 +90418,7 @@
         <v>522</v>
       </c>
       <c r="E1762">
-        <v>-0.908941043395461</v>
+        <v>-0.9051667470818865</v>
       </c>
       <c r="F1762">
         <v>-1</v>
@@ -90427,10 +90427,10 @@
         <v>0.008908552302378267</v>
       </c>
       <c r="H1762">
-        <v>0.009228941043395462</v>
+        <v>0.009205166747081887</v>
       </c>
       <c r="I1762">
-        <v>0.1203887410171935</v>
+        <v>0.116614444703619</v>
       </c>
       <c r="J1762">
         <v>1.377429631357462</v>
@@ -90442,10 +90442,10 @@
         <v>4.06</v>
       </c>
       <c r="M1762">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="N1762">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="O1762">
         <v>1</v>
@@ -90718,7 +90718,7 @@
         <v>522</v>
       </c>
       <c r="E1768">
-        <v>-1.20351700286766</v>
+        <v>-1.198942228403345</v>
       </c>
       <c r="F1768">
         <v>-1</v>
@@ -90727,10 +90727,10 @@
         <v>0.009278619709295889</v>
       </c>
       <c r="H1768">
-        <v>0.00952351700286766</v>
+        <v>0.009498942228403346</v>
       </c>
       <c r="I1768">
-        <v>0.1048972935717707</v>
+        <v>0.1003225191074559</v>
       </c>
       <c r="J1768">
         <v>1.457477446431429</v>
@@ -90742,10 +90742,10 @@
         <v>4.09</v>
       </c>
       <c r="M1768">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="N1768">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="O1768">
         <v>1</v>
@@ -91018,7 +91018,7 @@
         <v>522</v>
       </c>
       <c r="E1774">
-        <v>0.04412201583541364</v>
+        <v>0.04530646687933881</v>
       </c>
       <c r="F1774">
         <v>-1</v>
@@ -91027,10 +91027,10 @@
         <v>0.007853897805978598</v>
       </c>
       <c r="H1774">
-        <v>0.008275877984164588</v>
+        <v>0.008254693533120663</v>
       </c>
       <c r="I1774">
-        <v>0.1819801781859884</v>
+        <v>0.1807957271420633</v>
       </c>
       <c r="J1774">
         <v>1.118445104392551</v>
@@ -91042,10 +91042,10 @@
         <v>4.04</v>
       </c>
       <c r="M1774">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="N1774">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="O1774">
         <v>1</v>
@@ -91118,7 +91118,7 @@
         <v>522</v>
       </c>
       <c r="E1776">
-        <v>-0.3556560378230484</v>
+        <v>-0.3533852333724417</v>
       </c>
       <c r="F1776">
         <v>-1</v>
@@ -91127,10 +91127,10 @@
         <v>0.008379323166613351</v>
       </c>
       <c r="H1776">
-        <v>0.008675656037823051</v>
+        <v>0.008653385233372444</v>
       </c>
       <c r="I1776">
-        <v>0.09633287120969758</v>
+        <v>0.09406206675909079</v>
       </c>
       <c r="J1776">
         <v>1.227080445060611</v>
@@ -91142,10 +91142,10 @@
         <v>4.06</v>
       </c>
       <c r="M1776">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="N1776">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="O1776">
         <v>1</v>

--- a/s60_signal/position-00386-600028.xlsx
+++ b/s60_signal/position-00386-600028.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5346" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5343" uniqueCount="661">
   <si>
     <t>trade_time</t>
   </si>
@@ -1048,13 +1048,13 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-09-28</t>
-  </si>
-  <si>
     <t>2021-10-11</t>
   </si>
   <si>
     <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>2021-09-28</t>
   </si>
   <si>
     <t>2021-09-09</t>
@@ -1582,7 +1582,7 @@
     <t>2021-12-08</t>
   </si>
   <si>
-    <t>2021-12-15</t>
+    <t>2021-12-16</t>
   </si>
   <si>
     <t>2016-03-23</t>
@@ -2354,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1778"/>
+  <dimension ref="A1:P1777"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -82759,10 +82759,10 @@
         <v>7</v>
       </c>
       <c r="B1609" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C1609">
-        <v>2.131891436368013</v>
+        <v>2.152612161909092</v>
       </c>
       <c r="D1609" t="s">
         <v>516</v>
@@ -82774,19 +82774,19 @@
         <v>1</v>
       </c>
       <c r="G1609">
-        <v>0.006048108563631987</v>
+        <v>0.006027387838090908</v>
       </c>
       <c r="H1609">
         <v>0.005948243666229702</v>
       </c>
       <c r="I1609">
-        <v>0.1798648974022847</v>
+        <v>0.1591441718612061</v>
       </c>
       <c r="J1609">
         <v>0.5180181385269806</v>
       </c>
       <c r="K1609">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="L1609">
         <v>4.09</v>
@@ -83509,10 +83509,10 @@
         <v>7</v>
       </c>
       <c r="B1624" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C1624">
-        <v>1.867490072129021</v>
+        <v>1.869949752816273</v>
       </c>
       <c r="D1624" t="s">
         <v>348</v>
@@ -83524,22 +83524,22 @@
         <v>1</v>
       </c>
       <c r="G1624">
-        <v>0.006312509927870979</v>
+        <v>0.006410050247183726</v>
       </c>
       <c r="H1624">
         <v>0.006066406110705892</v>
       </c>
       <c r="I1624">
-        <v>0.1461038171650868</v>
+        <v>0.1436441364778349</v>
       </c>
       <c r="J1624">
         <v>0.5942539914093525</v>
       </c>
       <c r="K1624">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="L1624">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="M1624">
         <v>3.41</v>
@@ -84709,43 +84709,43 @@
         <v>1</v>
       </c>
       <c r="B1648" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C1648">
-        <v>0.916645161290325</v>
+        <v>0.9632903225806473</v>
       </c>
       <c r="D1648" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E1648">
-        <v>1.096365591397852</v>
+        <v>1.15877419354839</v>
       </c>
       <c r="F1648">
         <v>1</v>
       </c>
       <c r="G1648">
-        <v>0.007843354838709675</v>
+        <v>0.007036709677419353</v>
       </c>
       <c r="H1648">
-        <v>0.007303634408602148</v>
+        <v>0.006981225806451612</v>
       </c>
       <c r="I1648">
-        <v>0.1797204301075266</v>
+        <v>0.1954838709677422</v>
       </c>
       <c r="J1648">
         <v>0.8365591397849457</v>
       </c>
       <c r="K1648">
-        <v>4.14</v>
+        <v>3.63</v>
       </c>
       <c r="L1648">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="M1648">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="N1648">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="O1648">
         <v>1</v>
@@ -84759,43 +84759,43 @@
         <v>2</v>
       </c>
       <c r="B1649" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="C1649">
-        <v>0.9632903225806473</v>
+        <v>1.233956989247314</v>
       </c>
       <c r="D1649" t="s">
-        <v>514</v>
+        <v>347</v>
       </c>
       <c r="E1649">
-        <v>1.15877419354839</v>
+        <v>1.471075268817207</v>
       </c>
       <c r="F1649">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1649">
-        <v>0.007036709677419353</v>
+        <v>0.007826043010752686</v>
       </c>
       <c r="H1649">
-        <v>0.006981225806451612</v>
+        <v>0.007828924731182794</v>
       </c>
       <c r="I1649">
-        <v>0.1954838709677422</v>
+        <v>-0.2371182795698927</v>
       </c>
       <c r="J1649">
         <v>0.8365591397849457</v>
       </c>
       <c r="K1649">
-        <v>3.63</v>
+        <v>3.94</v>
       </c>
       <c r="L1649">
-        <v>4</v>
+        <v>4.53</v>
       </c>
       <c r="M1649">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="N1649">
-        <v>4.07</v>
+        <v>4.65</v>
       </c>
       <c r="O1649">
         <v>1</v>
@@ -84809,43 +84809,43 @@
         <v>3</v>
       </c>
       <c r="B1650" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="C1650">
-        <v>1.233956989247314</v>
+        <v>0.9627096774193573</v>
       </c>
       <c r="D1650" t="s">
-        <v>347</v>
+        <v>512</v>
       </c>
       <c r="E1650">
-        <v>1.471075268817207</v>
+        <v>1.101655913978496</v>
       </c>
       <c r="F1650">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1650">
-        <v>0.007826043010752686</v>
+        <v>0.007337290322580643</v>
       </c>
       <c r="H1650">
-        <v>0.007828924731182794</v>
+        <v>0.007158344086021504</v>
       </c>
       <c r="I1650">
-        <v>-0.2371182795698927</v>
+        <v>0.1389462365591392</v>
       </c>
       <c r="J1650">
         <v>0.8365591397849457</v>
       </c>
       <c r="K1650">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="L1650">
-        <v>4.53</v>
+        <v>4.15</v>
       </c>
       <c r="M1650">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="N1650">
-        <v>4.65</v>
+        <v>4.13</v>
       </c>
       <c r="O1650">
         <v>1</v>
@@ -84859,10 +84859,10 @@
         <v>4</v>
       </c>
       <c r="B1651" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1651">
-        <v>0.9627096774193573</v>
+        <v>0.9443440860215073</v>
       </c>
       <c r="D1651" t="s">
         <v>512</v>
@@ -84874,22 +84874,22 @@
         <v>1</v>
       </c>
       <c r="G1651">
-        <v>0.007337290322580643</v>
+        <v>0.007335655913978492</v>
       </c>
       <c r="H1651">
         <v>0.007158344086021504</v>
       </c>
       <c r="I1651">
-        <v>0.1389462365591392</v>
+        <v>0.1573118279569892</v>
       </c>
       <c r="J1651">
         <v>0.8365591397849457</v>
       </c>
       <c r="K1651">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="L1651">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="M1651">
         <v>3.62</v>
@@ -84906,96 +84906,96 @@
     </row>
     <row r="1652" spans="1:16">
       <c r="A1652" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1652" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C1652">
-        <v>0.9443440860215073</v>
+        <v>0.7718387076132496</v>
       </c>
       <c r="D1652" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="E1652">
-        <v>1.101655913978496</v>
+        <v>0.9386317121072669</v>
       </c>
       <c r="F1652">
         <v>1</v>
       </c>
       <c r="G1652">
-        <v>0.007335655913978492</v>
+        <v>0.008068161292386751</v>
       </c>
       <c r="H1652">
-        <v>0.007158344086021504</v>
+        <v>0.007461368287892734</v>
       </c>
       <c r="I1652">
-        <v>0.1573118279569892</v>
+        <v>0.1667930044940173</v>
       </c>
       <c r="J1652">
-        <v>0.8365591397849457</v>
+        <v>0.8790750102136747</v>
       </c>
       <c r="K1652">
-        <v>3.82</v>
+        <v>4.15</v>
       </c>
       <c r="L1652">
-        <v>4.14</v>
+        <v>4.42</v>
       </c>
       <c r="M1652">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="N1652">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
       <c r="O1652">
         <v>1</v>
       </c>
       <c r="P1652" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="1653" spans="1:16">
       <c r="A1653" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1653" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="C1653">
-        <v>0.7718387076132496</v>
+        <v>1.066444459758122</v>
       </c>
       <c r="D1653" t="s">
-        <v>517</v>
+        <v>347</v>
       </c>
       <c r="E1653">
-        <v>0.9386317121072669</v>
+        <v>1.309514961188036</v>
       </c>
       <c r="F1653">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1653">
-        <v>0.008068161292386751</v>
+        <v>0.007993555540241878</v>
       </c>
       <c r="H1653">
-        <v>0.007461368287892734</v>
+        <v>0.007990485038811964</v>
       </c>
       <c r="I1653">
-        <v>0.1667930044940173</v>
+        <v>-0.2430705014299144</v>
       </c>
       <c r="J1653">
         <v>0.8790750102136747</v>
       </c>
       <c r="K1653">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="L1653">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="M1653">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="N1653">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="O1653">
         <v>1</v>
@@ -85006,46 +85006,46 @@
     </row>
     <row r="1654" spans="1:16">
       <c r="A1654" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1654" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="C1654">
-        <v>1.066444459758122</v>
+        <v>0.8007242110858996</v>
       </c>
       <c r="D1654" t="s">
-        <v>347</v>
+        <v>512</v>
       </c>
       <c r="E1654">
-        <v>1.309514961188036</v>
+        <v>0.9477484630264974</v>
       </c>
       <c r="F1654">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1654">
-        <v>0.007993555540241878</v>
+        <v>0.007499275788914101</v>
       </c>
       <c r="H1654">
-        <v>0.007990485038811964</v>
+        <v>0.007312251536973502</v>
       </c>
       <c r="I1654">
-        <v>-0.2430705014299144</v>
+        <v>0.1470242519405978</v>
       </c>
       <c r="J1654">
         <v>0.8790750102136747</v>
       </c>
       <c r="K1654">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="L1654">
-        <v>4.53</v>
+        <v>4.15</v>
       </c>
       <c r="M1654">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="N1654">
-        <v>4.65</v>
+        <v>4.13</v>
       </c>
       <c r="O1654">
         <v>1</v>
@@ -85056,13 +85056,13 @@
     </row>
     <row r="1655" spans="1:16">
       <c r="A1655" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1655" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1655">
-        <v>0.8007242110858996</v>
+        <v>0.7819334609837623</v>
       </c>
       <c r="D1655" t="s">
         <v>512</v>
@@ -85074,22 +85074,22 @@
         <v>1</v>
       </c>
       <c r="G1655">
-        <v>0.007499275788914101</v>
+        <v>0.007498066539016237</v>
       </c>
       <c r="H1655">
         <v>0.007312251536973502</v>
       </c>
       <c r="I1655">
-        <v>0.1470242519405978</v>
+        <v>0.1658150020427351</v>
       </c>
       <c r="J1655">
         <v>0.8790750102136747</v>
       </c>
       <c r="K1655">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="L1655">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="M1655">
         <v>3.62</v>
@@ -85106,57 +85106,57 @@
     </row>
     <row r="1656" spans="1:16">
       <c r="A1656" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1656" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C1656">
-        <v>0.7819334609837623</v>
+        <v>0.8538868357141789</v>
       </c>
       <c r="D1656" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E1656">
-        <v>0.9477484630264974</v>
+        <v>1.053891511924337</v>
       </c>
       <c r="F1656">
         <v>1</v>
       </c>
       <c r="G1656">
-        <v>0.007498066539016237</v>
+        <v>0.007146113164285821</v>
       </c>
       <c r="H1656">
-        <v>0.007312251536973502</v>
+        <v>0.007086108488075664</v>
       </c>
       <c r="I1656">
-        <v>0.1658150020427351</v>
+        <v>0.2000046762101579</v>
       </c>
       <c r="J1656">
-        <v>0.8790750102136747</v>
+        <v>0.8666978414010527</v>
       </c>
       <c r="K1656">
-        <v>3.82</v>
+        <v>3.63</v>
       </c>
       <c r="L1656">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="M1656">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="N1656">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="O1656">
         <v>1</v>
       </c>
       <c r="P1656" t="s">
-        <v>648</v>
+        <v>341</v>
       </c>
     </row>
     <row r="1657" spans="1:16">
       <c r="A1657" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1657" t="s">
         <v>317</v>
@@ -85206,7 +85206,7 @@
     </row>
     <row r="1658" spans="1:16">
       <c r="A1658" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1658" t="s">
         <v>342</v>
@@ -85256,7 +85256,7 @@
     </row>
     <row r="1659" spans="1:16">
       <c r="A1659" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1659" t="s">
         <v>335</v>
@@ -87059,10 +87059,10 @@
         <v>1</v>
       </c>
       <c r="B1695" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C1695">
-        <v>1.030165556623081</v>
+        <v>1.032226275193106</v>
       </c>
       <c r="D1695" t="s">
         <v>514</v>
@@ -87074,22 +87074,22 @@
         <v>1</v>
       </c>
       <c r="G1695">
-        <v>0.00706983444337692</v>
+        <v>0.006907773724806894</v>
       </c>
       <c r="H1695">
         <v>0.006925713006236869</v>
       </c>
       <c r="I1695">
-        <v>0.1841214371400506</v>
+        <v>0.1820607185700251</v>
       </c>
       <c r="J1695">
         <v>0.8206071857002497</v>
       </c>
       <c r="K1695">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="L1695">
-        <v>4.05</v>
+        <v>3.97</v>
       </c>
       <c r="M1695">
         <v>3.48</v>
@@ -87109,43 +87109,43 @@
         <v>2</v>
       </c>
       <c r="B1696" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C1696">
-        <v>1.315777329056004</v>
+        <v>1.030165556623081</v>
       </c>
       <c r="D1696" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="E1696">
-        <v>1.098104838053056</v>
+        <v>1.214286993763131</v>
       </c>
       <c r="F1696">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1696">
-        <v>0.007864222670943997</v>
+        <v>0.00706983444337692</v>
       </c>
       <c r="H1696">
-        <v>0.007301895161946944</v>
+        <v>0.006925713006236869</v>
       </c>
       <c r="I1696">
-        <v>0.2176724910029471</v>
+        <v>0.1841214371400506</v>
       </c>
       <c r="J1696">
         <v>0.8206071857002497</v>
       </c>
       <c r="K1696">
-        <v>3.99</v>
+        <v>3.68</v>
       </c>
       <c r="L1696">
-        <v>4.59</v>
+        <v>4.05</v>
       </c>
       <c r="M1696">
-        <v>3.78</v>
+        <v>3.48</v>
       </c>
       <c r="N1696">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="O1696">
         <v>1</v>
@@ -87159,43 +87159,43 @@
         <v>3</v>
       </c>
       <c r="B1697" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C1697">
-        <v>1.023486622482049</v>
+        <v>1.315777329056004</v>
       </c>
       <c r="D1697" t="s">
-        <v>350</v>
+        <v>506</v>
       </c>
       <c r="E1697">
-        <v>1.168638418907111</v>
+        <v>1.098104838053056</v>
       </c>
       <c r="F1697">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1697">
-        <v>0.007276513377517952</v>
+        <v>0.007864222670943997</v>
       </c>
       <c r="H1697">
-        <v>0.007011361581092889</v>
+        <v>0.007301895161946944</v>
       </c>
       <c r="I1697">
-        <v>0.1451517964250617</v>
+        <v>0.2176724910029471</v>
       </c>
       <c r="J1697">
         <v>0.8206071857002497</v>
       </c>
       <c r="K1697">
-        <v>3.81</v>
+        <v>3.99</v>
       </c>
       <c r="L1697">
-        <v>4.15</v>
+        <v>4.59</v>
       </c>
       <c r="M1697">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="N1697">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="O1697">
         <v>1</v>
@@ -87209,10 +87209,10 @@
         <v>4</v>
       </c>
       <c r="B1698" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C1698">
-        <v>1.005280550625046</v>
+        <v>1.023486622482049</v>
       </c>
       <c r="D1698" t="s">
         <v>350</v>
@@ -87224,22 +87224,22 @@
         <v>1</v>
       </c>
       <c r="G1698">
-        <v>0.007274719449374954</v>
+        <v>0.007276513377517952</v>
       </c>
       <c r="H1698">
         <v>0.007011361581092889</v>
       </c>
       <c r="I1698">
-        <v>0.1633578682820649</v>
+        <v>0.1451517964250617</v>
       </c>
       <c r="J1698">
         <v>0.8206071857002497</v>
       </c>
       <c r="K1698">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="L1698">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="M1698">
         <v>3.56</v>
@@ -87256,96 +87256,96 @@
     </row>
     <row r="1699" spans="1:16">
       <c r="A1699" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1699" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C1699">
-        <v>0.9571010209057413</v>
+        <v>1.005280550625046</v>
       </c>
       <c r="D1699" t="s">
-        <v>514</v>
+        <v>350</v>
       </c>
       <c r="E1699">
-        <v>1.145193356726082</v>
+        <v>1.168638418907111</v>
       </c>
       <c r="F1699">
         <v>1</v>
       </c>
       <c r="G1699">
-        <v>0.007142898979094259</v>
+        <v>0.007274719449374954</v>
       </c>
       <c r="H1699">
-        <v>0.006994806643273919</v>
+        <v>0.007011361581092889</v>
       </c>
       <c r="I1699">
-        <v>0.1880923358203406</v>
+        <v>0.1633578682820649</v>
       </c>
       <c r="J1699">
-        <v>0.8404616791017007</v>
+        <v>0.8206071857002497</v>
       </c>
       <c r="K1699">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="L1699">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="M1699">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="N1699">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="O1699">
         <v>1</v>
       </c>
       <c r="P1699" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="1700" spans="1:16">
       <c r="A1700" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1700" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C1700">
-        <v>1.236557900384214</v>
+        <v>0.9571010209057413</v>
       </c>
       <c r="D1700" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E1700">
-        <v>1.091771750757265</v>
+        <v>1.145193356726082</v>
       </c>
       <c r="F1700">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1700">
-        <v>0.007943442099615785</v>
+        <v>0.007142898979094259</v>
       </c>
       <c r="H1700">
-        <v>0.007748228249242734</v>
+        <v>0.006994806643273919</v>
       </c>
       <c r="I1700">
-        <v>0.1447861496269489</v>
+        <v>0.1880923358203406</v>
       </c>
       <c r="J1700">
         <v>0.8404616791017007</v>
       </c>
       <c r="K1700">
-        <v>3.99</v>
+        <v>3.68</v>
       </c>
       <c r="L1700">
-        <v>4.59</v>
+        <v>4.05</v>
       </c>
       <c r="M1700">
-        <v>3.96</v>
+        <v>3.48</v>
       </c>
       <c r="N1700">
-        <v>4.42</v>
+        <v>4.07</v>
       </c>
       <c r="O1700">
         <v>1</v>
@@ -87356,46 +87356,46 @@
     </row>
     <row r="1701" spans="1:16">
       <c r="A1701" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1701" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C1701">
-        <v>0.9478410026225208</v>
+        <v>1.236557900384214</v>
       </c>
       <c r="D1701" t="s">
-        <v>350</v>
+        <v>518</v>
       </c>
       <c r="E1701">
-        <v>1.097956422397945</v>
+        <v>1.091771750757265</v>
       </c>
       <c r="F1701">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1701">
-        <v>0.007352158997377479</v>
+        <v>0.007943442099615785</v>
       </c>
       <c r="H1701">
-        <v>0.007082043577602054</v>
+        <v>0.007748228249242734</v>
       </c>
       <c r="I1701">
-        <v>0.1501154197754246</v>
+        <v>0.1447861496269489</v>
       </c>
       <c r="J1701">
         <v>0.8404616791017007</v>
       </c>
       <c r="K1701">
-        <v>3.81</v>
+        <v>3.99</v>
       </c>
       <c r="L1701">
-        <v>4.15</v>
+        <v>4.59</v>
       </c>
       <c r="M1701">
-        <v>3.56</v>
+        <v>3.96</v>
       </c>
       <c r="N1701">
-        <v>4.09</v>
+        <v>4.42</v>
       </c>
       <c r="O1701">
         <v>1</v>
@@ -87406,13 +87406,13 @@
     </row>
     <row r="1702" spans="1:16">
       <c r="A1702" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1702" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C1702">
-        <v>0.9294363858315031</v>
+        <v>0.9478410026225208</v>
       </c>
       <c r="D1702" t="s">
         <v>350</v>
@@ -87424,22 +87424,22 @@
         <v>1</v>
       </c>
       <c r="G1702">
-        <v>0.007350563614168497</v>
+        <v>0.007352158997377479</v>
       </c>
       <c r="H1702">
         <v>0.007082043577602054</v>
       </c>
       <c r="I1702">
-        <v>0.1685200365664423</v>
+        <v>0.1501154197754246</v>
       </c>
       <c r="J1702">
         <v>0.8404616791017007</v>
       </c>
       <c r="K1702">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="L1702">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="M1702">
         <v>3.56</v>
@@ -87456,96 +87456,96 @@
     </row>
     <row r="1703" spans="1:16">
       <c r="A1703" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1703" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C1703">
-        <v>0.8322487992326195</v>
+        <v>0.9294363858315031</v>
       </c>
       <c r="D1703" t="s">
-        <v>514</v>
+        <v>350</v>
       </c>
       <c r="E1703">
-        <v>1.027126581883021</v>
+        <v>1.097956422397945</v>
       </c>
       <c r="F1703">
         <v>1</v>
       </c>
       <c r="G1703">
-        <v>0.00726775120076738</v>
+        <v>0.007350563614168497</v>
       </c>
       <c r="H1703">
-        <v>0.00711287341811698</v>
+        <v>0.007082043577602054</v>
       </c>
       <c r="I1703">
-        <v>0.1948777826504018</v>
+        <v>0.1685200365664423</v>
       </c>
       <c r="J1703">
-        <v>0.8743889132520055</v>
+        <v>0.8404616791017007</v>
       </c>
       <c r="K1703">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="L1703">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="M1703">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="N1703">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="O1703">
         <v>1</v>
       </c>
       <c r="P1703" t="s">
-        <v>653</v>
+        <v>312</v>
       </c>
     </row>
     <row r="1704" spans="1:16">
       <c r="A1704" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1704" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C1704">
-        <v>1.303651570919619</v>
+        <v>0.8322487992326195</v>
       </c>
       <c r="D1704" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E1704">
-        <v>0.9574199035220583</v>
+        <v>1.027126581883021</v>
       </c>
       <c r="F1704">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1704">
-        <v>0.008176348429080381</v>
+        <v>0.00726775120076738</v>
       </c>
       <c r="H1704">
-        <v>0.007882580096477942</v>
+        <v>0.00711287341811698</v>
       </c>
       <c r="I1704">
-        <v>0.3462316673975603</v>
+        <v>0.1948777826504018</v>
       </c>
       <c r="J1704">
         <v>0.8743889132520055</v>
       </c>
       <c r="K1704">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="L1704">
-        <v>4.74</v>
+        <v>4.05</v>
       </c>
       <c r="M1704">
-        <v>3.96</v>
+        <v>3.48</v>
       </c>
       <c r="N1704">
-        <v>4.42</v>
+        <v>4.07</v>
       </c>
       <c r="O1704">
         <v>1</v>
@@ -87556,10 +87556,10 @@
     </row>
     <row r="1705" spans="1:16">
       <c r="A1705" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1705" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C1705">
         <v>1.104956568726938</v>
@@ -87606,7 +87606,7 @@
     </row>
     <row r="1706" spans="1:16">
       <c r="A1706" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1706" t="s">
         <v>342</v>
@@ -87656,7 +87656,7 @@
     </row>
     <row r="1707" spans="1:16">
       <c r="A1707" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1707" t="s">
         <v>335</v>
@@ -87759,7 +87759,7 @@
         <v>1</v>
       </c>
       <c r="B1709" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1709">
         <v>1.086709739738112</v>
@@ -87809,7 +87809,7 @@
         <v>2</v>
       </c>
       <c r="B1710" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1710">
         <v>1.177645223768056</v>
@@ -88009,7 +88009,7 @@
         <v>1</v>
       </c>
       <c r="B1714" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1714">
         <v>1.075192045545668</v>
@@ -88059,7 +88059,7 @@
         <v>2</v>
       </c>
       <c r="B1715" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1715">
         <v>1.166098147702673</v>
@@ -88259,7 +88259,7 @@
         <v>1</v>
       </c>
       <c r="B1719" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1719">
         <v>1.091379159187004</v>
@@ -88309,7 +88309,7 @@
         <v>2</v>
       </c>
       <c r="B1720" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1720">
         <v>1.182326555001257</v>
@@ -88509,7 +88509,7 @@
         <v>1</v>
       </c>
       <c r="B1724" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1724">
         <v>1.117564255676052</v>
@@ -88559,7 +88559,7 @@
         <v>2</v>
       </c>
       <c r="B1725" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1725">
         <v>1.208578450205838</v>
@@ -88759,7 +88759,7 @@
         <v>1</v>
       </c>
       <c r="B1729" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1729">
         <v>1.495250426632718</v>
@@ -88809,7 +88809,7 @@
         <v>2</v>
       </c>
       <c r="B1730" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1730">
         <v>1.587228106292496</v>
@@ -88959,7 +88959,7 @@
         <v>1</v>
       </c>
       <c r="B1733" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1733">
         <v>1.080935368626179</v>
@@ -89009,7 +89009,7 @@
         <v>2</v>
       </c>
       <c r="B1734" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1734">
         <v>1.171856122117572</v>
@@ -89159,7 +89159,7 @@
         <v>1</v>
       </c>
       <c r="B1737" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1737">
         <v>0.8836795062876304</v>
@@ -89209,7 +89209,7 @@
         <v>2</v>
       </c>
       <c r="B1738" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1738">
         <v>0.9740970560485684</v>
@@ -89309,7 +89309,7 @@
         <v>0</v>
       </c>
       <c r="B1740" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1740">
         <v>0.5654719323990891</v>
@@ -89359,7 +89359,7 @@
         <v>1</v>
       </c>
       <c r="B1741" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1741">
         <v>0.6550777281450051</v>
@@ -89459,7 +89459,7 @@
         <v>0</v>
       </c>
       <c r="B1743" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1743">
         <v>0.1601997621878715</v>
@@ -89509,7 +89509,7 @@
         <v>1</v>
       </c>
       <c r="B1744" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1744">
         <v>0.248771700356718</v>
@@ -89659,7 +89659,7 @@
         <v>0</v>
       </c>
       <c r="B1747" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1747">
         <v>-0.1264582701062222</v>
@@ -89709,7 +89709,7 @@
         <v>1</v>
       </c>
       <c r="B1748" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1748">
         <v>-0.03861760242792123</v>
@@ -89809,43 +89809,43 @@
         <v>3</v>
       </c>
       <c r="B1750" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C1750">
-        <v>-0.5048649468892261</v>
+        <v>-0.1063323216995453</v>
       </c>
       <c r="D1750" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="E1750">
-        <v>-0.2716783004552354</v>
+        <v>-0.3154309559939303</v>
       </c>
       <c r="F1750">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1750">
-        <v>0.008784864946889225</v>
+        <v>0.008186332321699545</v>
       </c>
       <c r="H1750">
-        <v>0.008531678300455236</v>
+        <v>0.00875543095599393</v>
       </c>
       <c r="I1750">
-        <v>0.2331866464339907</v>
+        <v>0.209098634294385</v>
       </c>
       <c r="J1750">
         <v>1.215933232169955</v>
       </c>
       <c r="K1750">
-        <v>3.82</v>
+        <v>3.41</v>
       </c>
       <c r="L1750">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
       <c r="M1750">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="N1750">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
       <c r="O1750">
         <v>1</v>
@@ -89856,63 +89856,63 @@
     </row>
     <row r="1751" spans="1:16">
       <c r="A1751" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1751" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C1751">
-        <v>-0.1063323216995453</v>
+        <v>-0.4832316420284801</v>
       </c>
       <c r="D1751" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E1751">
-        <v>-0.3154309559939303</v>
+        <v>-0.7308568582995418</v>
       </c>
       <c r="F1751">
         <v>-1</v>
       </c>
       <c r="G1751">
-        <v>0.008186332321699545</v>
+        <v>0.00976323164202848</v>
       </c>
       <c r="H1751">
-        <v>0.00875543095599393</v>
+        <v>0.009750856858299543</v>
       </c>
       <c r="I1751">
-        <v>0.209098634294385</v>
+        <v>0.2476252162710617</v>
       </c>
       <c r="J1751">
-        <v>1.215933232169955</v>
+        <v>1.306946847456245</v>
       </c>
       <c r="K1751">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="L1751">
-        <v>4.04</v>
+        <v>4.64</v>
       </c>
       <c r="M1751">
-        <v>3.73</v>
+        <v>4.01</v>
       </c>
       <c r="N1751">
-        <v>4.22</v>
+        <v>4.51</v>
       </c>
       <c r="O1751">
         <v>1</v>
       </c>
       <c r="P1751" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="1752" spans="1:16">
       <c r="A1752" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1752" t="s">
         <v>346</v>
       </c>
       <c r="C1752">
-        <v>-0.4832316420284801</v>
+        <v>-0.3963011105030425</v>
       </c>
       <c r="D1752" t="s">
         <v>520</v>
@@ -89924,22 +89924,22 @@
         <v>-1</v>
       </c>
       <c r="G1752">
-        <v>0.00976323164202848</v>
+        <v>0.009876301110503043</v>
       </c>
       <c r="H1752">
         <v>0.009750856858299543</v>
       </c>
       <c r="I1752">
-        <v>0.2476252162710617</v>
+        <v>0.3345557477964993</v>
       </c>
       <c r="J1752">
         <v>1.306946847456245</v>
       </c>
       <c r="K1752">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="L1752">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
       <c r="M1752">
         <v>4.01</v>
@@ -89956,46 +89956,46 @@
     </row>
     <row r="1753" spans="1:16">
       <c r="A1753" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1753" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C1753">
-        <v>-0.3963011105030425</v>
+        <v>-0.8294674888082927</v>
       </c>
       <c r="D1753" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="E1753">
-        <v>-0.7308568582995418</v>
+        <v>-0.6011475877916066</v>
       </c>
       <c r="F1753">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1753">
-        <v>0.009876301110503043</v>
+        <v>0.009129467488808293</v>
       </c>
       <c r="H1753">
-        <v>0.009750856858299543</v>
+        <v>0.008861147587791607</v>
       </c>
       <c r="I1753">
-        <v>0.3345557477964993</v>
+        <v>0.2283199010166861</v>
       </c>
       <c r="J1753">
         <v>1.306946847456245</v>
       </c>
       <c r="K1753">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="L1753">
-        <v>4.74</v>
+        <v>4.15</v>
       </c>
       <c r="M1753">
-        <v>4.01</v>
+        <v>3.62</v>
       </c>
       <c r="N1753">
-        <v>4.51</v>
+        <v>4.13</v>
       </c>
       <c r="O1753">
         <v>1</v>
@@ -90006,13 +90006,13 @@
     </row>
     <row r="1754" spans="1:16">
       <c r="A1754" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1754" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1754">
-        <v>-0.8294674888082927</v>
+        <v>-0.8525369572828554</v>
       </c>
       <c r="D1754" t="s">
         <v>512</v>
@@ -90024,22 +90024,22 @@
         <v>1</v>
       </c>
       <c r="G1754">
-        <v>0.009129467488808293</v>
+        <v>0.009132536957282856</v>
       </c>
       <c r="H1754">
         <v>0.008861147587791607</v>
       </c>
       <c r="I1754">
-        <v>0.2283199010166861</v>
+        <v>0.2513893694912488</v>
       </c>
       <c r="J1754">
         <v>1.306946847456245</v>
       </c>
       <c r="K1754">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="L1754">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="M1754">
         <v>3.62</v>
@@ -90056,46 +90056,46 @@
     </row>
     <row r="1755" spans="1:16">
       <c r="A1755" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1755" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C1755">
-        <v>-0.8525369572828554</v>
+        <v>-0.416688749825795</v>
       </c>
       <c r="D1755" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="E1755">
-        <v>-0.6011475877916066</v>
+        <v>-0.6157033355881065</v>
       </c>
       <c r="F1755">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1755">
-        <v>0.009132536957282856</v>
+        <v>0.008496688749825796</v>
       </c>
       <c r="H1755">
-        <v>0.008861147587791607</v>
+        <v>0.009055703335588106</v>
       </c>
       <c r="I1755">
-        <v>0.2513893694912488</v>
+        <v>0.1990145857623116</v>
       </c>
       <c r="J1755">
         <v>1.306946847456245</v>
       </c>
       <c r="K1755">
-        <v>3.82</v>
+        <v>3.41</v>
       </c>
       <c r="L1755">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
       <c r="M1755">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="N1755">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
       <c r="O1755">
         <v>1</v>
@@ -90106,63 +90106,63 @@
     </row>
     <row r="1756" spans="1:16">
       <c r="A1756" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1756" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C1756">
-        <v>-0.416688749825795</v>
+        <v>-0.7595241549212526</v>
       </c>
       <c r="D1756" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E1756">
-        <v>-0.6464949301644181</v>
+        <v>-1.013492821743424</v>
       </c>
       <c r="F1756">
         <v>-1</v>
       </c>
       <c r="G1756">
-        <v>0.008496688749825796</v>
+        <v>0.01003952415492125</v>
       </c>
       <c r="H1756">
-        <v>0.00894649493016442</v>
+        <v>0.01003349282174342</v>
       </c>
       <c r="I1756">
-        <v>0.2298061803386231</v>
+        <v>0.2539686668221712</v>
       </c>
       <c r="J1756">
-        <v>1.306946847456245</v>
+        <v>1.377429631357462</v>
       </c>
       <c r="K1756">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="L1756">
-        <v>4.04</v>
+        <v>4.64</v>
       </c>
       <c r="M1756">
-        <v>3.67</v>
+        <v>4.01</v>
       </c>
       <c r="N1756">
-        <v>4.15</v>
+        <v>4.51</v>
       </c>
       <c r="O1756">
         <v>1</v>
       </c>
       <c r="P1756" t="s">
-        <v>659</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1757" spans="1:16">
       <c r="A1757" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1757" t="s">
         <v>346</v>
       </c>
       <c r="C1757">
-        <v>-0.7595241549212526</v>
+        <v>-0.6732984512348272</v>
       </c>
       <c r="D1757" t="s">
         <v>520</v>
@@ -90174,22 +90174,22 @@
         <v>-1</v>
       </c>
       <c r="G1757">
-        <v>0.01003952415492125</v>
+        <v>0.01015329845123483</v>
       </c>
       <c r="H1757">
         <v>0.01003349282174342</v>
       </c>
       <c r="I1757">
-        <v>0.2539686668221712</v>
+        <v>0.3401943705085966</v>
       </c>
       <c r="J1757">
         <v>1.377429631357462</v>
       </c>
       <c r="K1757">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="L1757">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
       <c r="M1757">
         <v>4.01</v>
@@ -90206,46 +90206,46 @@
     </row>
     <row r="1758" spans="1:16">
       <c r="A1758" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1758" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C1758">
-        <v>-0.6732984512348272</v>
+        <v>-1.098006895471931</v>
       </c>
       <c r="D1758" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="E1758">
-        <v>-1.013492821743424</v>
+        <v>-0.8562952655140137</v>
       </c>
       <c r="F1758">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1758">
-        <v>0.01015329845123483</v>
+        <v>0.009398006895471931</v>
       </c>
       <c r="H1758">
-        <v>0.01003349282174342</v>
+        <v>0.009116295265514014</v>
       </c>
       <c r="I1758">
-        <v>0.3401943705085966</v>
+        <v>0.2417116299579174</v>
       </c>
       <c r="J1758">
         <v>1.377429631357462</v>
       </c>
       <c r="K1758">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="L1758">
-        <v>4.74</v>
+        <v>4.15</v>
       </c>
       <c r="M1758">
-        <v>4.01</v>
+        <v>3.62</v>
       </c>
       <c r="N1758">
-        <v>4.51</v>
+        <v>4.13</v>
       </c>
       <c r="O1758">
         <v>1</v>
@@ -90256,13 +90256,13 @@
     </row>
     <row r="1759" spans="1:16">
       <c r="A1759" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1759" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1759">
-        <v>-1.098006895471931</v>
+        <v>-1.121781191785506</v>
       </c>
       <c r="D1759" t="s">
         <v>512</v>
@@ -90274,22 +90274,22 @@
         <v>1</v>
       </c>
       <c r="G1759">
-        <v>0.009398006895471931</v>
+        <v>0.009401781191785507</v>
       </c>
       <c r="H1759">
         <v>0.009116295265514014</v>
       </c>
       <c r="I1759">
-        <v>0.2417116299579174</v>
+        <v>0.2654859262714924</v>
       </c>
       <c r="J1759">
         <v>1.377429631357462</v>
       </c>
       <c r="K1759">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="L1759">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="M1759">
         <v>3.62</v>
@@ -90306,13 +90306,13 @@
     </row>
     <row r="1760" spans="1:16">
       <c r="A1760" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1760" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C1760">
-        <v>-1.121781191785506</v>
+        <v>-1.116684006531208</v>
       </c>
       <c r="D1760" t="s">
         <v>512</v>
@@ -90324,22 +90324,22 @@
         <v>1</v>
       </c>
       <c r="G1760">
-        <v>0.009401781191785507</v>
+        <v>0.009296684006531209</v>
       </c>
       <c r="H1760">
         <v>0.009116295265514014</v>
       </c>
       <c r="I1760">
-        <v>0.2654859262714924</v>
+        <v>0.2603887410171941</v>
       </c>
       <c r="J1760">
         <v>1.377429631357462</v>
       </c>
       <c r="K1760">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="L1760">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="M1760">
         <v>3.62</v>
@@ -90356,46 +90356,46 @@
     </row>
     <row r="1761" spans="1:16">
       <c r="A1761" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1761" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="C1761">
-        <v>-1.116684006531208</v>
+        <v>-0.7885523023782675</v>
       </c>
       <c r="D1761" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="E1761">
-        <v>-0.8562952655140137</v>
+        <v>-0.8764896360226109</v>
       </c>
       <c r="F1761">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1761">
-        <v>0.009296684006531209</v>
+        <v>0.008908552302378267</v>
       </c>
       <c r="H1761">
-        <v>0.009116295265514014</v>
+        <v>0.00931648963602261</v>
       </c>
       <c r="I1761">
-        <v>0.2603887410171941</v>
+        <v>0.08793733364434342</v>
       </c>
       <c r="J1761">
         <v>1.377429631357462</v>
       </c>
       <c r="K1761">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="L1761">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="M1761">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="N1761">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
       <c r="O1761">
         <v>1</v>
@@ -90406,63 +90406,63 @@
     </row>
     <row r="1762" spans="1:16">
       <c r="A1762" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1762" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C1762">
-        <v>-0.7885523023782675</v>
+        <v>-1.073311590011203</v>
       </c>
       <c r="D1762" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E1762">
-        <v>-0.9051667470818865</v>
+        <v>-1.334484560190031</v>
       </c>
       <c r="F1762">
         <v>-1</v>
       </c>
       <c r="G1762">
-        <v>0.008908552302378267</v>
+        <v>0.0103533115900112</v>
       </c>
       <c r="H1762">
-        <v>0.009205166747081887</v>
+        <v>0.01035448456019003</v>
       </c>
       <c r="I1762">
-        <v>0.116614444703619</v>
+        <v>0.2611729701788281</v>
       </c>
       <c r="J1762">
-        <v>1.377429631357462</v>
+        <v>1.457477446431429</v>
       </c>
       <c r="K1762">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="L1762">
-        <v>4.06</v>
+        <v>4.64</v>
       </c>
       <c r="M1762">
-        <v>3.67</v>
+        <v>4.01</v>
       </c>
       <c r="N1762">
-        <v>4.15</v>
+        <v>4.51</v>
       </c>
       <c r="O1762">
         <v>1</v>
       </c>
       <c r="P1762" t="s">
-        <v>519</v>
+        <v>660</v>
       </c>
     </row>
     <row r="1763" spans="1:16">
       <c r="A1763" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1763" t="s">
         <v>346</v>
       </c>
       <c r="C1763">
-        <v>-1.073311590011203</v>
+        <v>-0.9878863644755169</v>
       </c>
       <c r="D1763" t="s">
         <v>520</v>
@@ -90474,22 +90474,22 @@
         <v>-1</v>
       </c>
       <c r="G1763">
-        <v>0.0103533115900112</v>
+        <v>0.01046788636447552</v>
       </c>
       <c r="H1763">
         <v>0.01035448456019003</v>
       </c>
       <c r="I1763">
-        <v>0.2611729701788281</v>
+        <v>0.3465981957145141</v>
       </c>
       <c r="J1763">
         <v>1.457477446431429</v>
       </c>
       <c r="K1763">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="L1763">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
       <c r="M1763">
         <v>4.01</v>
@@ -90506,46 +90506,46 @@
     </row>
     <row r="1764" spans="1:16">
       <c r="A1764" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1764" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C1764">
-        <v>-0.9878863644755169</v>
+        <v>-1.402989070903745</v>
       </c>
       <c r="D1764" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="E1764">
-        <v>-1.334484560190031</v>
+        <v>-1.146068356081774</v>
       </c>
       <c r="F1764">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1764">
-        <v>0.01046788636447552</v>
+        <v>0.009702989070903745</v>
       </c>
       <c r="H1764">
-        <v>0.01035448456019003</v>
+        <v>0.009406068356081775</v>
       </c>
       <c r="I1764">
-        <v>0.3465981957145141</v>
+        <v>0.2569207148219705</v>
       </c>
       <c r="J1764">
         <v>1.457477446431429</v>
       </c>
       <c r="K1764">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="L1764">
-        <v>4.74</v>
+        <v>4.15</v>
       </c>
       <c r="M1764">
-        <v>4.01</v>
+        <v>3.62</v>
       </c>
       <c r="N1764">
-        <v>4.51</v>
+        <v>4.13</v>
       </c>
       <c r="O1764">
         <v>1</v>
@@ -90556,13 +90556,13 @@
     </row>
     <row r="1765" spans="1:16">
       <c r="A1765" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1765" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1765">
-        <v>-1.402989070903745</v>
+        <v>-1.42756384536806</v>
       </c>
       <c r="D1765" t="s">
         <v>512</v>
@@ -90574,22 +90574,22 @@
         <v>1</v>
       </c>
       <c r="G1765">
-        <v>0.009702989070903745</v>
+        <v>0.009707563845368061</v>
       </c>
       <c r="H1765">
         <v>0.009406068356081775</v>
       </c>
       <c r="I1765">
-        <v>0.2569207148219705</v>
+        <v>0.2814954892862858</v>
       </c>
       <c r="J1765">
         <v>1.457477446431429</v>
       </c>
       <c r="K1765">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="L1765">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="M1765">
         <v>3.62</v>
@@ -90606,13 +90606,13 @@
     </row>
     <row r="1766" spans="1:16">
       <c r="A1766" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1766" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C1766">
-        <v>-1.42756384536806</v>
+        <v>-1.419264747510803</v>
       </c>
       <c r="D1766" t="s">
         <v>512</v>
@@ -90624,22 +90624,22 @@
         <v>1</v>
       </c>
       <c r="G1766">
-        <v>0.009707563845368061</v>
+        <v>0.009599264747510801</v>
       </c>
       <c r="H1766">
         <v>0.009406068356081775</v>
       </c>
       <c r="I1766">
-        <v>0.2814954892862858</v>
+        <v>0.2731963914290283</v>
       </c>
       <c r="J1766">
         <v>1.457477446431429</v>
       </c>
       <c r="K1766">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="L1766">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="M1766">
         <v>3.62</v>
@@ -90656,46 +90656,46 @@
     </row>
     <row r="1767" spans="1:16">
       <c r="A1767" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1767" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C1767">
-        <v>-1.419264747510803</v>
+        <v>-1.098619709295889</v>
       </c>
       <c r="D1767" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="E1767">
-        <v>-1.146068356081774</v>
+        <v>-1.172666551796289</v>
       </c>
       <c r="F1767">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1767">
-        <v>0.009599264747510801</v>
+        <v>0.009278619709295889</v>
       </c>
       <c r="H1767">
-        <v>0.009406068356081775</v>
+        <v>0.009612666551796288</v>
       </c>
       <c r="I1767">
-        <v>0.2731963914290283</v>
+        <v>0.07404684250040017</v>
       </c>
       <c r="J1767">
         <v>1.457477446431429</v>
       </c>
       <c r="K1767">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="L1767">
         <v>4.09</v>
       </c>
       <c r="M1767">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="N1767">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
       <c r="O1767">
         <v>1</v>
@@ -90706,63 +90706,63 @@
     </row>
     <row r="1768" spans="1:16">
       <c r="A1768" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1768" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C1768">
-        <v>-1.098619709295889</v>
+        <v>-1.714778218876519</v>
       </c>
       <c r="D1768" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="E1768">
-        <v>-1.198942228403345</v>
+        <v>-1.561633269398798</v>
       </c>
       <c r="F1768">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1768">
-        <v>0.009278619709295889</v>
+        <v>0.01001477821887652</v>
       </c>
       <c r="H1768">
-        <v>0.009498942228403346</v>
+        <v>0.009921633269398798</v>
       </c>
       <c r="I1768">
-        <v>0.1003225191074559</v>
+        <v>0.1531449494777215</v>
       </c>
       <c r="J1768">
-        <v>1.457477446431429</v>
+        <v>1.539311868471527</v>
       </c>
       <c r="K1768">
-        <v>3.56</v>
+        <v>3.81</v>
       </c>
       <c r="L1768">
-        <v>4.09</v>
+        <v>4.15</v>
       </c>
       <c r="M1768">
-        <v>3.67</v>
+        <v>3.73</v>
       </c>
       <c r="N1768">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="O1768">
         <v>1</v>
       </c>
       <c r="P1768" t="s">
-        <v>660</v>
+        <v>346</v>
       </c>
     </row>
     <row r="1769" spans="1:16">
       <c r="A1769" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1769" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1769">
-        <v>-1.714778218876519</v>
+        <v>-1.740171337561235</v>
       </c>
       <c r="D1769" t="s">
         <v>511</v>
@@ -90774,22 +90774,22 @@
         <v>1</v>
       </c>
       <c r="G1769">
-        <v>0.01001477821887652</v>
+        <v>0.01002017133756123</v>
       </c>
       <c r="H1769">
         <v>0.009921633269398798</v>
       </c>
       <c r="I1769">
-        <v>0.1531449494777215</v>
+        <v>0.1785380681624371</v>
       </c>
       <c r="J1769">
         <v>1.539311868471527</v>
       </c>
       <c r="K1769">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="L1769">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="M1769">
         <v>3.73</v>
@@ -90801,18 +90801,18 @@
         <v>1</v>
       </c>
       <c r="P1769" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="1770" spans="1:16">
       <c r="A1770" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1770" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C1770">
-        <v>-1.740171337561235</v>
+        <v>-1.728598862822373</v>
       </c>
       <c r="D1770" t="s">
         <v>511</v>
@@ -90824,22 +90824,22 @@
         <v>1</v>
       </c>
       <c r="G1770">
-        <v>0.01002017133756123</v>
+        <v>0.009908598862822374</v>
       </c>
       <c r="H1770">
         <v>0.009921633269398798</v>
       </c>
       <c r="I1770">
-        <v>0.1785380681624371</v>
+        <v>0.1669655934235754</v>
       </c>
       <c r="J1770">
         <v>1.539311868471527</v>
       </c>
       <c r="K1770">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="L1770">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="M1770">
         <v>3.73</v>
@@ -90851,151 +90851,151 @@
         <v>1</v>
       </c>
       <c r="P1770" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="1771" spans="1:16">
       <c r="A1771" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1771" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C1771">
-        <v>-1.728598862822373</v>
+        <v>-1.389950251758638</v>
       </c>
       <c r="D1771" t="s">
-        <v>511</v>
+        <v>348</v>
       </c>
       <c r="E1771">
-        <v>-1.561633269398798</v>
+        <v>-1.209053471487909</v>
       </c>
       <c r="F1771">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1771">
-        <v>0.009908598862822374</v>
+        <v>0.009569950251758637</v>
       </c>
       <c r="H1771">
-        <v>0.009921633269398798</v>
+        <v>0.00928905347148791</v>
       </c>
       <c r="I1771">
-        <v>0.1669655934235754</v>
+        <v>-0.1808967802707286</v>
       </c>
       <c r="J1771">
         <v>1.539311868471527</v>
       </c>
       <c r="K1771">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="L1771">
         <v>4.09</v>
       </c>
       <c r="M1771">
-        <v>3.73</v>
+        <v>3.41</v>
       </c>
       <c r="N1771">
-        <v>4.18</v>
+        <v>4.04</v>
       </c>
       <c r="O1771">
         <v>1</v>
       </c>
       <c r="P1771" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="1772" spans="1:16">
       <c r="A1772" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1772" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="C1772">
-        <v>-1.389950251758638</v>
+        <v>-0.1377224946038416</v>
       </c>
       <c r="D1772" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1772">
-        <v>-1.209053471487909</v>
+        <v>0.08122872209896581</v>
       </c>
       <c r="F1772">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1772">
-        <v>0.009569950251758637</v>
+        <v>0.008317722494603842</v>
       </c>
       <c r="H1772">
-        <v>0.00928905347148791</v>
+        <v>0.008178771277901035</v>
       </c>
       <c r="I1772">
-        <v>-0.1808967802707286</v>
+        <v>0.2189512167028074</v>
       </c>
       <c r="J1772">
-        <v>1.539311868471527</v>
+        <v>1.118445104392551</v>
       </c>
       <c r="K1772">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="L1772">
         <v>4.09</v>
       </c>
       <c r="M1772">
-        <v>3.41</v>
+        <v>3.62</v>
       </c>
       <c r="N1772">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="O1772">
         <v>1</v>
       </c>
       <c r="P1772" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="1773" spans="1:16">
       <c r="A1773" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1773" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="C1773">
-        <v>-0.1377224946038416</v>
+        <v>0.2261021940214021</v>
       </c>
       <c r="D1773" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E1773">
-        <v>0.008199760615785756</v>
+        <v>0.08175311374756156</v>
       </c>
       <c r="F1773">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1773">
-        <v>0.008317722494603842</v>
+        <v>0.007853897805978598</v>
       </c>
       <c r="H1773">
-        <v>0.008351800239384215</v>
+        <v>0.008358246886252437</v>
       </c>
       <c r="I1773">
-        <v>0.1459222552196273</v>
+        <v>0.1443490802738405</v>
       </c>
       <c r="J1773">
         <v>1.118445104392551</v>
       </c>
       <c r="K1773">
-        <v>3.78</v>
+        <v>3.41</v>
       </c>
       <c r="L1773">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="M1773">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="N1773">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="O1773">
         <v>1</v>
@@ -91006,96 +91006,96 @@
     </row>
     <row r="1774" spans="1:16">
       <c r="A1774" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1774" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="C1774">
-        <v>0.2261021940214021</v>
+        <v>-0.5483640823291092</v>
       </c>
       <c r="D1774" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E1774">
-        <v>0.04530646687933881</v>
+        <v>-0.3120312111194119</v>
       </c>
       <c r="F1774">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1774">
-        <v>0.007853897805978598</v>
+        <v>0.008728364082329108</v>
       </c>
       <c r="H1774">
-        <v>0.008254693533120663</v>
+        <v>0.008572031211119413</v>
       </c>
       <c r="I1774">
-        <v>0.1807957271420633</v>
+        <v>0.2363328712096973</v>
       </c>
       <c r="J1774">
-        <v>1.118445104392551</v>
+        <v>1.227080445060611</v>
       </c>
       <c r="K1774">
-        <v>3.41</v>
+        <v>3.78</v>
       </c>
       <c r="L1774">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="M1774">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="N1774">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="O1774">
         <v>1</v>
       </c>
       <c r="P1774" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1775" spans="1:16">
       <c r="A1775" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1775" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="C1775">
-        <v>-0.5483640823291092</v>
+        <v>-0.2593231666133509</v>
       </c>
       <c r="D1775" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="E1775">
-        <v>-0.3120312111194119</v>
+        <v>-0.3201976467242611</v>
       </c>
       <c r="F1775">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1775">
-        <v>0.008728364082329108</v>
+        <v>0.008379323166613351</v>
       </c>
       <c r="H1775">
-        <v>0.008572031211119413</v>
+        <v>0.008760197646724262</v>
       </c>
       <c r="I1775">
-        <v>0.2363328712096973</v>
+        <v>0.06087448011091023</v>
       </c>
       <c r="J1775">
         <v>1.227080445060611</v>
       </c>
       <c r="K1775">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="L1775">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="M1775">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="N1775">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
       <c r="O1775">
         <v>1</v>
@@ -91106,34 +91106,34 @@
     </row>
     <row r="1776" spans="1:16">
       <c r="A1776" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1776" t="s">
         <v>349</v>
       </c>
       <c r="C1776">
-        <v>-0.2593231666133509</v>
+        <v>-1.953911993830408</v>
       </c>
       <c r="D1776" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E1776">
-        <v>-0.3533852333724417</v>
+        <v>-2.152696516189608</v>
       </c>
       <c r="F1776">
         <v>-1</v>
       </c>
       <c r="G1776">
-        <v>0.008379323166613351</v>
+        <v>0.01007391199383041</v>
       </c>
       <c r="H1776">
-        <v>0.008653385233372444</v>
+        <v>0.01059269651618961</v>
       </c>
       <c r="I1776">
-        <v>0.09406206675909079</v>
+        <v>0.1987845223592002</v>
       </c>
       <c r="J1776">
-        <v>1.227080445060611</v>
+        <v>1.708497725520002</v>
       </c>
       <c r="K1776">
         <v>3.52</v>
@@ -91142,16 +91142,16 @@
         <v>4.06</v>
       </c>
       <c r="M1776">
-        <v>3.67</v>
+        <v>3.73</v>
       </c>
       <c r="N1776">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="O1776">
         <v>1</v>
       </c>
       <c r="P1776" t="s">
-        <v>340</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1777" spans="1:16">
@@ -91162,28 +91162,28 @@
         <v>349</v>
       </c>
       <c r="C1777">
-        <v>-1.953911993830408</v>
+        <v>-3.115552841470282</v>
       </c>
       <c r="D1777" t="s">
-        <v>521</v>
+        <v>348</v>
       </c>
       <c r="E1777">
-        <v>-2.152696516189608</v>
+        <v>-2.911316815174336</v>
       </c>
       <c r="F1777">
         <v>-1</v>
       </c>
       <c r="G1777">
-        <v>0.01007391199383041</v>
+        <v>0.01123555284147028</v>
       </c>
       <c r="H1777">
-        <v>0.01059269651618961</v>
+        <v>0.01099131681517434</v>
       </c>
       <c r="I1777">
-        <v>0.1987845223592002</v>
+        <v>-0.2042360262959457</v>
       </c>
       <c r="J1777">
-        <v>1.708497725520002</v>
+        <v>2.038509329963148</v>
       </c>
       <c r="K1777">
         <v>3.52</v>
@@ -91192,65 +91192,15 @@
         <v>4.06</v>
       </c>
       <c r="M1777">
-        <v>3.73</v>
+        <v>3.41</v>
       </c>
       <c r="N1777">
-        <v>4.22</v>
+        <v>4.04</v>
       </c>
       <c r="O1777">
         <v>1</v>
       </c>
       <c r="P1777" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="1778" spans="1:16">
-      <c r="A1778" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1778" t="s">
-        <v>349</v>
-      </c>
-      <c r="C1778">
-        <v>-3.115552841470282</v>
-      </c>
-      <c r="D1778" t="s">
-        <v>348</v>
-      </c>
-      <c r="E1778">
-        <v>-2.911316815174336</v>
-      </c>
-      <c r="F1778">
-        <v>-1</v>
-      </c>
-      <c r="G1778">
-        <v>0.01123555284147028</v>
-      </c>
-      <c r="H1778">
-        <v>0.01099131681517434</v>
-      </c>
-      <c r="I1778">
-        <v>-0.2042360262959457</v>
-      </c>
-      <c r="J1778">
-        <v>2.038509329963148</v>
-      </c>
-      <c r="K1778">
-        <v>3.52</v>
-      </c>
-      <c r="L1778">
-        <v>4.06</v>
-      </c>
-      <c r="M1778">
-        <v>3.41</v>
-      </c>
-      <c r="N1778">
-        <v>4.04</v>
-      </c>
-      <c r="O1778">
-        <v>1</v>
-      </c>
-      <c r="P1778" t="s">
         <v>510</v>
       </c>
     </row>
